--- a/assets/data.xlsx
+++ b/assets/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDEAPAD\OneDrive\Documents\Bahan Materi\2025-2026\Code\Web\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D820BF-15AF-44A9-A5F4-0D1991BAB6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757A0358-919D-411D-85A5-805F1B410B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B09C82DE-86FE-4D12-8009-001B53EF35FD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="107">
   <si>
     <t>Nama</t>
   </si>
@@ -436,7 +436,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -462,19 +462,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -906,7 +893,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B2" t="s">
@@ -915,7 +902,7 @@
       <c r="C2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="10">
         <v>85</v>
       </c>
       <c r="E2" t="str">
@@ -924,7 +911,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B3" t="s">
@@ -933,16 +920,16 @@
       <c r="C3" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>106</v>
+      <c r="D3" s="10">
+        <v>88</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E66" si="0">IF(D3="-","Kamu Belum Mengerjakan Tugas 😒","Tugasmu Sudah Selesai 😊")</f>
-        <v>Kamu Belum Mengerjakan Tugas 😒</v>
+        <v>Tugasmu Sudah Selesai 😊</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B4" t="s">
@@ -951,7 +938,7 @@
       <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E4" t="str">
@@ -960,7 +947,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B5" t="s">
@@ -969,7 +956,7 @@
       <c r="C5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="10">
         <v>90</v>
       </c>
       <c r="E5" t="str">
@@ -978,7 +965,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B6" t="s">
@@ -987,7 +974,7 @@
       <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E6" t="str">
@@ -996,7 +983,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B7" t="s">
@@ -1005,7 +992,7 @@
       <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E7" t="str">
@@ -1014,7 +1001,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B8" t="s">
@@ -1023,7 +1010,7 @@
       <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E8" t="str">
@@ -1032,7 +1019,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B9" t="s">
@@ -1041,7 +1028,7 @@
       <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="10">
         <v>95</v>
       </c>
       <c r="E9" t="str">
@@ -1050,7 +1037,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B10" t="s">
@@ -1059,7 +1046,7 @@
       <c r="C10" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="10">
         <v>95</v>
       </c>
       <c r="E10" t="str">
@@ -1068,7 +1055,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B11" t="s">
@@ -1077,7 +1064,7 @@
       <c r="C11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E11" t="str">
@@ -1086,7 +1073,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B12" t="s">
@@ -1095,7 +1082,7 @@
       <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="10">
         <v>92</v>
       </c>
       <c r="E12" t="str">
@@ -1104,7 +1091,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B13" t="s">
@@ -1113,7 +1100,7 @@
       <c r="C13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="10">
         <v>92</v>
       </c>
       <c r="E13" t="str">
@@ -1122,7 +1109,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B14" t="s">
@@ -1131,7 +1118,7 @@
       <c r="C14" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E14" t="str">
@@ -1140,7 +1127,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B15" t="s">
@@ -1149,7 +1136,7 @@
       <c r="C15" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E15" t="str">
@@ -1158,7 +1145,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B16" t="s">
@@ -1167,7 +1154,7 @@
       <c r="C16" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="10">
         <v>88</v>
       </c>
       <c r="E16" t="str">
@@ -1176,7 +1163,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B17" t="s">
@@ -1185,7 +1172,7 @@
       <c r="C17" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="10">
         <v>98</v>
       </c>
       <c r="E17" t="str">
@@ -1194,7 +1181,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B18" t="s">
@@ -1203,7 +1190,7 @@
       <c r="C18" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="10">
         <v>95</v>
       </c>
       <c r="E18" t="str">
@@ -1212,7 +1199,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B19" t="s">
@@ -1221,7 +1208,7 @@
       <c r="C19" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="10">
         <v>88</v>
       </c>
       <c r="E19" t="str">
@@ -1230,7 +1217,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B20" t="s">
@@ -1239,7 +1226,7 @@
       <c r="C20" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="10">
         <v>95</v>
       </c>
       <c r="E20" t="str">
@@ -1248,7 +1235,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B21" t="s">
@@ -1257,7 +1244,7 @@
       <c r="C21" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="10">
         <v>90</v>
       </c>
       <c r="E21" t="str">
@@ -1266,7 +1253,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B22" t="s">
@@ -1275,7 +1262,7 @@
       <c r="C22" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E22" t="str">
@@ -1284,7 +1271,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B23" t="s">
@@ -1293,7 +1280,7 @@
       <c r="C23" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E23" t="str">
@@ -1302,7 +1289,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B24" t="s">
@@ -1311,7 +1298,7 @@
       <c r="C24" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E24" t="str">
@@ -1320,7 +1307,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B25" t="s">
@@ -1329,7 +1316,7 @@
       <c r="C25" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E25" t="str">
@@ -1338,7 +1325,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B26" t="s">
@@ -1347,7 +1334,7 @@
       <c r="C26" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E26" t="str">
@@ -1356,7 +1343,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B27" t="s">
@@ -1365,7 +1352,7 @@
       <c r="C27" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="10">
         <v>88</v>
       </c>
       <c r="E27" t="str">
@@ -1374,7 +1361,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B28" t="s">
@@ -1383,7 +1370,7 @@
       <c r="C28" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E28" t="str">
@@ -1392,7 +1379,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B29" t="s">
@@ -1401,7 +1388,7 @@
       <c r="C29" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E29" t="str">
@@ -1410,7 +1397,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B30" t="s">
@@ -1419,7 +1406,7 @@
       <c r="C30" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E30" t="str">
@@ -1428,7 +1415,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B31" t="s">
@@ -1437,7 +1424,7 @@
       <c r="C31" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E31" t="str">
@@ -1446,7 +1433,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="4" t="s">
         <v>103</v>
       </c>
       <c r="B32" t="s">
@@ -1455,7 +1442,7 @@
       <c r="C32" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E32" t="str">
@@ -1464,7 +1451,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B33" t="s">
@@ -1473,7 +1460,7 @@
       <c r="C33" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="10">
         <v>90</v>
       </c>
       <c r="E33" t="str">
@@ -2193,12 +2180,12 @@
       <c r="C73" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D73" s="7" t="s">
-        <v>106</v>
+      <c r="D73" s="7">
+        <v>85</v>
       </c>
       <c r="E73" t="str">
         <f t="shared" si="1"/>
-        <v>Kamu Belum Mengerjakan Tugas 😒</v>
+        <v>Tugasmu Sudah Selesai 😊</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
@@ -2553,7 +2540,7 @@
       <c r="C93" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D93" s="14" t="s">
+      <c r="D93" s="10" t="s">
         <v>106</v>
       </c>
       <c r="E93" t="str">
